--- a/Handling-timeDE.xlsx
+++ b/Handling-timeDE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanignaciomartinez/Desktop/StockAmazon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C91C321-C412-6645-8071-28B9E9E5E4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06541D1-900F-CB4A-8711-0906FB5681D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{D9964971-FD87-6A4B-96D8-DE1421DA450B}"/>
   </bookViews>
@@ -485,7 +485,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
